--- a/scripts/factory_test_results.xlsx
+++ b/scripts/factory_test_results.xlsx
@@ -56,9 +56,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,42 +485,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-07-30 11:05:55</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 11:07:34</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>W2MLaserTOY</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>A4:C1:38:16:31:AB</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>0x425032303333371700CC084456036278</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
